--- a/publication/web-root/matchsync-donor/ValueSet-nmdp-hla-gene-name-vs.xlsx
+++ b/publication/web-root/matchsync-donor/ValueSet-nmdp-hla-gene-name-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:43:13+00:00</t>
+    <t>2026-09-22T13:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publication/web-root/matchsync-donor/ValueSet-nmdp-hla-gene-name-vs.xlsx
+++ b/publication/web-root/matchsync-donor/ValueSet-nmdp-hla-gene-name-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:14:09+00:00</t>
+    <t>2026-09-24T13:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
